--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>GCU Toastmasters</t>
+          <t>GCUF Toastmasters</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5655,8 +5655,8 @@
       <c r="T50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U50" s="9" t="n">
-        <v>0</v>
+      <c r="U50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V50" s="9" t="n">
         <v>0</v>
@@ -9550,8 +9550,8 @@
       <c r="W88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X88" s="9" t="n">
-        <v>0</v>
+      <c r="X88" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -10057,8 +10057,8 @@
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X93" s="9" t="n">
-        <v>1</v>
+      <c r="X93" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -15789,7 +15789,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>

--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,11 @@
       <c r="AB55" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC55" s="4" t="inlineStr"/>
+      <c r="AC55" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6378,7 +6382,11 @@
       <c r="AB57" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -6790,7 +6798,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7820,7 +7832,11 @@
       <c r="AB71" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8543,7 +8559,11 @@
       <c r="AB78" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -8749,7 +8769,11 @@
       <c r="AB80" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC80" s="4" t="inlineStr"/>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -9052,7 +9076,11 @@
       <c r="AB83" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC83" s="4" t="inlineStr"/>
+      <c r="AC83" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9565,7 +9593,11 @@
       <c r="AB88" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -9971,7 +10003,11 @@
       <c r="AB92" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC92" s="4" t="inlineStr"/>
+      <c r="AC92" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -10484,7 +10520,11 @@
       <c r="AB97" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC97" s="4" t="inlineStr"/>
+      <c r="AC97" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -10890,7 +10930,11 @@
       <c r="AB101" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11411,7 +11455,11 @@
       <c r="AB106" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC106" s="4" t="inlineStr"/>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11512,7 +11560,11 @@
       <c r="AB107" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC107" s="4" t="inlineStr"/>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11613,7 +11665,11 @@
       <c r="AB108" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11714,7 +11770,11 @@
       <c r="AB109" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -12017,7 +12077,11 @@
       <c r="AB112" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -14166,7 +14230,11 @@
       <c r="AB133" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC133" s="4" t="inlineStr"/>
+      <c r="AC133" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -15095,7 +15163,11 @@
       <c r="AB142" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC142" s="4" t="inlineStr"/>
+      <c r="AC142" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">

--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 115 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 112 clubs short</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="U35" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V35" s="9" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -4866,11 +4866,11 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" s="9" t="n">
-        <v>0</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W42" s="10" t="n">
+        <v>24</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>5</v>
@@ -4878,8 +4878,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="9" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="P59" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q59" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q59" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R59" s="9" t="n">
         <v>0</v>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8033,8 +8033,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11323,8 +11323,8 @@
       <c r="S105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U105" s="9" t="n">
         <v>0</v>
@@ -11341,8 +11341,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -15354,8 +15354,8 @@
       <c r="W144" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X144" s="9" t="n">
-        <v>0</v>
+      <c r="X144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
@@ -15795,7 +15795,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15927,7 +15927,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16026,7 +16026,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16257,7 +16257,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 112 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 97 clubs short</t>
         </is>
       </c>
     </row>
@@ -1042,11 +1042,11 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Contour Lahore Toastmasters Club</t>
+          <t>Contour Toastmasters Club</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="P4" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>0</v>
@@ -1116,8 +1116,8 @@
       <c r="Y4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="10" t="n">
         <v>1</v>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1413,8 +1413,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1611,8 +1611,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2502,8 +2502,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3393,8 +3393,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3960,8 +3960,8 @@
       <c r="P33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" s="9" t="n">
-        <v>1</v>
+      <c r="Q33" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="9" t="n">
         <v>0</v>
@@ -5656,7 +5656,7 @@
         <v>1</v>
       </c>
       <c r="U50" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V50" s="9" t="n">
         <v>0</v>
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6995,8 +6995,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7100,8 +7100,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="9" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7718,8 +7718,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -7922,8 +7922,8 @@
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X72" s="9" t="n">
-        <v>3</v>
+      <c r="X72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
@@ -8233,8 +8233,8 @@
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X75" s="9" t="n">
-        <v>0</v>
+      <c r="X75" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8439,8 +8439,8 @@
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X77" s="9" t="n">
-        <v>3</v>
+      <c r="X77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8544,8 +8544,8 @@
       <c r="W78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X78" s="9" t="n">
-        <v>3</v>
+      <c r="X78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -8649,8 +8649,8 @@
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X79" s="9" t="n">
-        <v>0</v>
+      <c r="X79" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8960,8 +8960,8 @@
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X82" s="9" t="n">
-        <v>0</v>
+      <c r="X82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
@@ -9061,8 +9061,8 @@
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X83" s="9" t="n">
-        <v>3</v>
+      <c r="X83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9267,14 +9267,14 @@
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X85" s="9" t="n">
-        <v>0</v>
+      <c r="X85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9372,8 +9372,8 @@
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X86" s="9" t="n">
-        <v>0</v>
+      <c r="X86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
@@ -9477,8 +9477,8 @@
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X87" s="9" t="n">
-        <v>2</v>
+      <c r="X87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9994,8 +9994,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10301,8 +10301,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10546,7 +10546,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10596,7 +10596,7 @@
         <v>0</v>
       </c>
       <c r="S98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" s="9" t="n">
         <v>0</v>
@@ -10616,8 +10616,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10921,8 +10921,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11075,13 +11075,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11119,8 +11119,8 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="9" t="n">
-        <v>1</v>
+      <c r="V103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -11376,7 +11376,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11446,8 +11446,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11495,13 +11495,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11911,13 +11911,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>4</v>
       </c>
       <c r="W111" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X111" s="9" t="n">
         <v>1</v>
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12146,8 +12146,8 @@
       <c r="P113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" s="9" t="n">
-        <v>1</v>
+      <c r="Q113" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12155,8 +12155,8 @@
       <c r="S113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T113" s="9" t="n">
-        <v>0</v>
+      <c r="T113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U113" s="9" t="n">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14011,8 +14011,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -15564,7 +15564,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15663,7 +15663,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15762,7 +15762,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15960,7 +15960,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -15993,7 +15993,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16125,7 +16125,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16158,7 +16158,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16191,7 +16191,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16224,7 +16224,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16257,7 +16257,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16323,7 +16323,7 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16422,7 +16422,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 97 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 94 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -961,17 +961,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M3" s="8" t="n">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1104,11 +1104,11 @@
       <c r="U4" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="9" t="n">
-        <v>0</v>
+      <c r="V4" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W4" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>5</v>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1357,17 +1357,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="8" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="10" t="n">
         <v>1</v>
@@ -1456,17 +1456,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>63</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-63</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="8" t="n">
@@ -1555,17 +1555,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1782,8 +1782,8 @@
       <c r="P11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="9" t="n">
-        <v>1</v>
+      <c r="Q11" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1951,13 +1951,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2050,13 +2050,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2347,17 +2347,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2446,17 +2446,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2644,17 +2644,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2688,11 +2688,11 @@
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>3</v>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>6</v>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2842,17 +2842,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-31</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
+        <v>-13</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3040,17 +3040,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M24" s="8" t="n">
@@ -3084,11 +3084,11 @@
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>3</v>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>4</v>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3535,13 +3535,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3733,17 +3733,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -3780,8 +3780,8 @@
       <c r="V31" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W31" s="9" t="n">
-        <v>3</v>
+      <c r="W31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X31" s="9" t="n">
         <v>3</v>
@@ -3789,8 +3789,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3931,13 +3931,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4030,17 +4030,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4078,10 +4078,10 @@
         <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X34" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="X34" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y34" s="9" t="n">
         <v>0</v>
@@ -4129,17 +4129,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4426,17 +4426,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M38" s="8" t="n">
@@ -4624,17 +4624,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4669,7 +4669,7 @@
         <v>1</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4822,13 +4822,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>4</v>
       </c>
       <c r="W42" s="10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X42" s="10" t="n">
         <v>5</v>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4966,13 +4966,13 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X43" s="9" t="n">
-        <v>1</v>
+      <c r="X43" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y43" s="9" t="n">
         <v>0</v>
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5119,17 +5119,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M45" s="8" t="n">
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5317,13 +5317,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5416,13 +5416,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5553,8 +5553,8 @@
       <c r="S49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T49" s="9" t="n">
-        <v>0</v>
+      <c r="T49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U49" s="9" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
         <v>4</v>
       </c>
       <c r="W49" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>5</v>
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5713,13 +5713,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5911,17 +5911,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6010,13 +6010,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6111,17 +6111,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6216,17 +6216,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6358,14 +6358,14 @@
       <c r="T57" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="9" t="n">
-        <v>3</v>
+      <c r="U57" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>6</v>
@@ -6422,13 +6422,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6523,17 +6523,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6567,8 +6567,8 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>3</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6628,17 +6628,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6733,17 +6733,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6939,17 +6939,17 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M63" s="8" t="n">
@@ -7044,17 +7044,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -7250,13 +7250,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7351,13 +7351,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7452,13 +7452,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7557,17 +7557,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7602,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7662,13 +7662,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7706,11 +7706,11 @@
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="9" t="n">
-        <v>0</v>
+      <c r="V70" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X70" s="10" t="n">
         <v>7</v>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7767,17 +7767,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -7814,8 +7814,8 @@
       <c r="V71" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W71" s="9" t="n">
-        <v>2</v>
+      <c r="W71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -7872,17 +7872,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -7977,17 +7977,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8022,7 +8022,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8082,13 +8082,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8183,17 +8183,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8389,13 +8389,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8494,17 +8494,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8599,13 +8599,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8704,17 +8704,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -8809,13 +8809,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8910,13 +8910,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -8954,11 +8954,11 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="9" t="n">
-        <v>3</v>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>4</v>
@@ -9011,17 +9011,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9116,13 +9116,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9217,17 +9217,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -9322,13 +9322,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9427,13 +9427,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9528,17 +9528,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9566,8 +9566,8 @@
       <c r="S88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
+      <c r="T88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U88" s="9" t="n">
         <v>0</v>
@@ -9732,13 +9732,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9833,13 +9833,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9938,17 +9938,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10043,13 +10043,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10245,17 +10245,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10350,13 +10350,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10455,13 +10455,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10499,11 +10499,11 @@
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>0</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X97" s="10" t="n">
         <v>4</v>
@@ -10605,7 +10605,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10661,13 +10661,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10760,17 +10760,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10865,13 +10865,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10909,8 +10909,8 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>0</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11075,17 +11075,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -11180,13 +11180,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11285,17 +11285,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11330,7 +11330,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11390,17 +11390,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11435,7 +11435,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11495,17 +11495,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11600,17 +11600,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11645,7 +11645,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11705,17 +11705,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11810,13 +11810,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11911,17 +11911,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -11998,7 +11998,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12012,17 +12012,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -12068,8 +12068,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12117,13 +12117,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12218,13 +12218,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12319,13 +12319,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12420,13 +12420,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12521,13 +12521,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12622,13 +12622,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12723,13 +12723,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12828,13 +12828,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -12929,13 +12929,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13034,13 +13034,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13135,17 +13135,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -13240,13 +13240,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13341,13 +13341,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13442,13 +13442,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13543,13 +13543,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13648,13 +13648,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13753,13 +13753,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13854,17 +13854,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -13899,7 +13899,7 @@
         <v>1</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13955,13 +13955,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -14060,13 +14060,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14165,13 +14165,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -14209,11 +14209,11 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="9" t="n">
-        <v>1</v>
+      <c r="V133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X133" s="10" t="n">
         <v>6</v>
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14371,13 +14371,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14472,17 +14472,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14577,17 +14577,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -14682,17 +14682,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
@@ -14787,13 +14787,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14888,13 +14888,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14993,13 +14993,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15098,17 +15098,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L142" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M142" s="8" t="n">
@@ -15146,7 +15146,7 @@
         <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X142" s="9" t="n">
         <v>1</v>
@@ -15154,8 +15154,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -15203,13 +15203,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15304,17 +15304,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -15352,7 +15352,7 @@
         <v>4</v>
       </c>
       <c r="W144" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>4</v>
@@ -15409,13 +15409,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15564,13 +15564,13 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -15579,7 +15579,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -15597,7 +15597,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15612,7 +15612,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -15645,7 +15645,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -15663,7 +15663,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15678,7 +15678,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -15696,7 +15696,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -15729,7 +15729,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15744,7 +15744,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15777,7 +15777,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -15810,7 +15810,7 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -15828,7 +15828,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15843,7 +15843,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -15876,7 +15876,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15894,7 +15894,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -15927,7 +15927,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -15975,7 +15975,7 @@
         <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -15993,7 +15993,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16008,7 +16008,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -16041,7 +16041,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -16074,7 +16074,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -16092,7 +16092,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16107,7 +16107,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -16125,7 +16125,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16140,7 +16140,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -16173,7 +16173,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -16191,7 +16191,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16206,7 +16206,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -16224,7 +16224,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16239,7 +16239,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -16272,7 +16272,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -16290,7 +16290,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -16305,7 +16305,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -16371,7 +16371,7 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -16422,7 +16422,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16437,7 +16437,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -16503,7 +16503,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -16521,7 +16521,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -16536,7 +16536,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 94 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 91 clubs short</t>
         </is>
       </c>
     </row>
@@ -912,8 +912,8 @@
       <c r="W2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X2" s="9" t="n">
-        <v>3</v>
+      <c r="X2" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y2" s="9" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
         <v>5</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1258,13 +1258,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1302,14 +1302,14 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>3</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X6" s="9" t="n">
-        <v>1</v>
+      <c r="X6" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y6" s="9" t="n">
         <v>0</v>
@@ -1407,8 +1407,8 @@
       <c r="W7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X7" s="9" t="n">
-        <v>3</v>
+      <c r="X7" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y7" s="9" t="n">
         <v>0</v>
@@ -1605,8 +1605,8 @@
       <c r="W9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>2</v>
+      <c r="X9" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y9" s="9" t="n">
         <v>0</v>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1803,8 +1803,8 @@
       <c r="W11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X11" s="9" t="n">
-        <v>0</v>
+      <c r="X11" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y11" s="9" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -2397,8 +2397,8 @@
       <c r="W17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>3</v>
+      <c r="X17" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y17" s="9" t="n">
         <v>0</v>
@@ -2496,8 +2496,8 @@
       <c r="W18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X18" s="9" t="n">
-        <v>1</v>
+      <c r="X18" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y18" s="9" t="n">
         <v>0</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>1</v>
@@ -2793,8 +2793,8 @@
       <c r="W21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X21" s="9" t="n">
-        <v>0</v>
+      <c r="X21" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>0</v>
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-31</v>
+        <v>-14</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2892,8 +2892,8 @@
       <c r="W22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X22" s="9" t="n">
-        <v>1</v>
+      <c r="X22" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y22" s="9" t="n">
         <v>0</v>
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3535,13 +3535,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3733,13 +3733,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3768,8 +3768,8 @@
       <c r="R31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S31" s="9" t="n">
-        <v>1</v>
+      <c r="S31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T31" s="10" t="n">
         <v>1</v>
@@ -4030,13 +4030,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -6111,13 +6111,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="P59" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q59" s="10" t="n">
         <v>2</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6733,17 +6733,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6760,7 +6760,7 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>0</v>
@@ -6771,8 +6771,8 @@
       <c r="S61" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T61" s="9" t="n">
-        <v>0</v>
+      <c r="T61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U61" s="9" t="n">
         <v>0</v>
@@ -6781,7 +6781,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -7977,13 +7977,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8494,13 +8494,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8655,8 +8655,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="9" t="n">
         <v>0</v>
@@ -9528,13 +9528,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9732,13 +9732,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>0</v>
@@ -9777,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9979,8 +9979,8 @@
       <c r="T92" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U92" s="9" t="n">
-        <v>0</v>
+      <c r="U92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V92" s="9" t="n">
         <v>1</v>
@@ -10043,13 +10043,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10560,13 +10560,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10865,13 +10865,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X101" s="10" t="n">
         <v>6</v>
@@ -10956,7 +10956,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11008,14 +11008,14 @@
       <c r="S102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T102" s="9" t="n">
-        <v>0</v>
+      <c r="T102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11075,13 +11075,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X103" s="9" t="n">
         <v>2</v>
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11180,13 +11180,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11224,8 +11224,8 @@
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="9" t="n">
-        <v>0</v>
+      <c r="V104" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11236,8 +11236,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -11315,7 +11315,7 @@
         <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
@@ -11390,13 +11390,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11627,7 +11627,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11796,7 +11796,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11810,13 +11810,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11854,8 +11854,8 @@
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>2</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11911,13 +11911,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12012,17 +12012,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L112" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-10</v>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -12057,7 +12057,7 @@
         <v>2</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -12153,7 +12153,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="10" t="n">
         <v>1</v>
@@ -12173,8 +12173,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="9" t="n">
         <v>0</v>
@@ -12723,13 +12723,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -13135,17 +13135,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L123" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -13626,11 +13626,11 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>1028833</v>
+        <v>7690269</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Progressive Toastmaster Club</t>
+          <t>Ohod Debate Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -13648,13 +13648,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13693,13 +13693,13 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X128" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13711,13 +13711,9 @@
         <v>1</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC128" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -13731,11 +13727,11 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>7690269</v>
+        <v>1028833</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Sijal Al-Ra'y Debate Club</t>
+          <t>Progressive Toastmaster Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13753,13 +13749,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13804,7 +13800,7 @@
         <v>0</v>
       </c>
       <c r="X129" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -13816,9 +13812,13 @@
         <v>1</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC129" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC129" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -13982,10 +13982,10 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
@@ -14060,13 +14060,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14165,13 +14165,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -14577,13 +14577,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14627,8 +14627,8 @@
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X137" s="9" t="n">
-        <v>1</v>
+      <c r="X137" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
@@ -14682,13 +14682,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-18</v>
+        <v>-10</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14888,13 +14888,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-16</v>
+        <v>-7</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15098,13 +15098,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15125,10 +15125,10 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
@@ -15145,11 +15145,11 @@
       <c r="V142" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W142" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X142" s="9" t="n">
-        <v>1</v>
+      <c r="W142" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X142" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
@@ -15203,13 +15203,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15253,8 +15253,8 @@
       <c r="W143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X143" s="9" t="n">
-        <v>0</v>
+      <c r="X143" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
@@ -15304,13 +15304,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15409,13 +15409,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -15729,13 +15729,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -15927,7 +15927,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15942,7 +15942,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -16158,7 +16158,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16224,7 +16224,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16257,7 +16257,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -16305,7 +16305,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -16371,7 +16371,7 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -16521,7 +16521,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/104/inyear.xlsx
+++ b/docs/d/104/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 22 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 22 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 91 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 84 clubs short</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1095,8 +1095,8 @@
       <c r="R4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S4" s="9" t="n">
-        <v>1</v>
+      <c r="S4" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T4" s="10" t="n">
         <v>1</v>
@@ -1209,8 +1209,8 @@
       <c r="W5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X5" s="9" t="n">
-        <v>2</v>
+      <c r="X5" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
@@ -1704,8 +1704,8 @@
       <c r="W10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X10" s="9" t="n">
-        <v>2</v>
+      <c r="X10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y10" s="9" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2194,13 +2194,13 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X15" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2347,17 +2347,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2403,8 +2403,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2898,8 +2898,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -2941,13 +2941,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -2986,13 +2986,13 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X23" s="9" t="n">
-        <v>1</v>
+      <c r="X23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y23" s="9" t="n">
         <v>0</v>
@@ -3189,8 +3189,8 @@
       <c r="W25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X25" s="9" t="n">
-        <v>1</v>
+      <c r="X25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y25" s="9" t="n">
         <v>0</v>
@@ -3486,8 +3486,8 @@
       <c r="W28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X28" s="9" t="n">
-        <v>3</v>
+      <c r="X28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y28" s="9" t="n">
         <v>0</v>
@@ -3684,8 +3684,8 @@
       <c r="W30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>1</v>
+      <c r="X30" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y30" s="9" t="n">
         <v>0</v>
@@ -3733,13 +3733,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3783,8 +3783,8 @@
       <c r="W31" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="X31" s="9" t="n">
-        <v>3</v>
+      <c r="X31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>0</v>
@@ -4278,8 +4278,8 @@
       <c r="W36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X36" s="9" t="n">
-        <v>2</v>
+      <c r="X36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y36" s="9" t="n">
         <v>0</v>
@@ -4575,8 +4575,8 @@
       <c r="W39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X39" s="9" t="n">
-        <v>2</v>
+      <c r="X39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y39" s="9" t="n">
         <v>0</v>
@@ -4674,8 +4674,8 @@
       <c r="W40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X40" s="9" t="n">
-        <v>3</v>
+      <c r="X40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y40" s="9" t="n">
         <v>0</v>
@@ -5268,8 +5268,8 @@
       <c r="W46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X46" s="9" t="n">
-        <v>3</v>
+      <c r="X46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y46" s="9" t="n">
         <v>0</v>
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>4</v>
       </c>
       <c r="W49" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>5</v>
@@ -5961,8 +5961,8 @@
       <c r="W53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X53" s="9" t="n">
-        <v>3</v>
+      <c r="X53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y53" s="9" t="n">
         <v>0</v>
@@ -6733,13 +6733,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8018,8 +8018,8 @@
       <c r="T73" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U73" s="9" t="n">
-        <v>0</v>
+      <c r="U73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V73" s="9" t="n">
         <v>1</v>
@@ -8338,8 +8338,8 @@
       <c r="W76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X76" s="9" t="n">
-        <v>0</v>
+      <c r="X76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8754,8 +8754,8 @@
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="9" t="n">
-        <v>0</v>
+      <c r="X80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -9166,8 +9166,8 @@
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="9" t="n">
-        <v>0</v>
+      <c r="X84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -9683,8 +9683,8 @@
       <c r="W89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X89" s="9" t="n">
-        <v>1</v>
+      <c r="X89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9718,7 +9718,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9788,8 +9788,8 @@
       <c r="Y90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" s="9" t="n">
-        <v>0</v>
+      <c r="Z90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA90" s="10" t="n">
         <v>1</v>
@@ -9883,8 +9883,8 @@
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X91" s="9" t="n">
-        <v>2</v>
+      <c r="X91" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -10194,8 +10194,8 @@
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X94" s="9" t="n">
-        <v>0</v>
+      <c r="X94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -10295,8 +10295,8 @@
       <c r="W95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X95" s="9" t="n">
-        <v>2</v>
+      <c r="X95" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -10400,8 +10400,8 @@
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X96" s="9" t="n">
-        <v>1</v>
+      <c r="X96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -10610,8 +10610,8 @@
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="9" t="n">
-        <v>2</v>
+      <c r="X98" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10711,8 +10711,8 @@
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X99" s="9" t="n">
-        <v>0</v>
+      <c r="X99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -11020,8 +11020,8 @@
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="9" t="n">
-        <v>0</v>
+      <c r="X102" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11125,8 +11125,8 @@
       <c r="W103" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="X103" s="9" t="n">
-        <v>2</v>
+      <c r="X103" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -11522,7 +11522,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>1</v>
@@ -11586,7 +11586,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11600,13 +11600,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11644,14 +11644,14 @@
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="9" t="n">
-        <v>3</v>
+      <c r="V108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="9" t="n">
-        <v>0</v>
+      <c r="X108" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11961,14 +11961,14 @@
       <c r="W111" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="X111" s="9" t="n">
-        <v>1</v>
+      <c r="X111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -12012,13 +12012,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12062,8 +12062,8 @@
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X112" s="9" t="n">
-        <v>0</v>
+      <c r="X112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -12117,13 +12117,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12162,13 +12162,13 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="9" t="n">
-        <v>0</v>
+      <c r="X113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12369,8 +12369,8 @@
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X115" s="9" t="n">
-        <v>0</v>
+      <c r="X115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -12470,8 +12470,8 @@
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="9" t="n">
-        <v>1</v>
+      <c r="X116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -13162,7 +13162,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -13185,8 +13185,8 @@
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="9" t="n">
-        <v>3</v>
+      <c r="X123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -13543,13 +13543,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14194,8 +14194,8 @@
       <c r="P133" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q133" s="9" t="n">
-        <v>1</v>
+      <c r="Q133" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -14270,13 +14270,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14315,13 +14315,13 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X134" s="9" t="n">
-        <v>0</v>
+      <c r="X134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -14421,8 +14421,8 @@
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X135" s="9" t="n">
-        <v>2</v>
+      <c r="X135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -14604,7 +14604,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14732,14 +14732,14 @@
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X138" s="9" t="n">
-        <v>0</v>
+      <c r="X138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14874,7 +14874,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14938,14 +14938,14 @@
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X140" s="9" t="n">
-        <v>3</v>
+      <c r="X140" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -14993,13 +14993,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-18</v>
+        <v>-15</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15043,8 +15043,8 @@
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X141" s="9" t="n">
-        <v>2</v>
+      <c r="X141" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
@@ -15189,7 +15189,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15259,8 +15259,8 @@
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -15459,8 +15459,8 @@
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X145" s="9" t="n">
-        <v>1</v>
+      <c r="X145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
@@ -15564,7 +15564,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -15630,7 +15630,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15645,7 +15645,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -15663,7 +15663,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16026,7 +16026,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16158,7 +16158,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16257,7 +16257,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -16422,7 +16422,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16488,7 +16488,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -16521,7 +16521,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
